--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.1896551724137931</v>
+        <v>0.2</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.01515151515151515</v>
       </c>
       <c r="C2">
-        <v>0.2071428571428572</v>
+        <v>0.1928571428571429</v>
       </c>
       <c r="D2">
-        <v>0.9098360655737705</v>
+        <v>0.8968253968253969</v>
       </c>
       <c r="E2">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G2">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
